--- a/Planilha Veículos c- depreciação.xlsx
+++ b/Planilha Veículos c- depreciação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\autualizaFipe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD96A998-DA3B-439C-AC50-75A117656C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D5AA78-D182-4B1B-914C-871304190EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7C20ADAB-4EB5-4DF2-B8FE-4F27C0C1DB8E}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EQUIPAMENTOS PESADOS'!$B$2:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">VEICULOS!$B$2:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">VEICULOS!$B$2:$N$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">VEICULOS!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="241">
   <si>
     <t xml:space="preserve">CÓD ATIVO </t>
   </si>
@@ -166,51 +166,30 @@
     <t>CAMINHAO BASCULANTE VOLKSWAGEM</t>
   </si>
   <si>
-    <t>VW - 31.320 6X4/ 14M³ (THR-6E50)</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
     <t>CBV-02</t>
   </si>
   <si>
-    <t>VW - 31.320 6X4/ 14M³ (THN-7F10)</t>
-  </si>
-  <si>
     <t>CBV-03</t>
   </si>
   <si>
-    <t>VW - 31.320 6X4/ 14M³ (THX-7G30)</t>
-  </si>
-  <si>
     <t>CBV-04</t>
   </si>
   <si>
-    <t>VW - 31.320 6X4/ 14M³ (TIL-8A36)</t>
-  </si>
-  <si>
     <t>CBV-05</t>
   </si>
   <si>
-    <t>VW - 31.320 6X4/ 14M³ (TIM-4C66)</t>
-  </si>
-  <si>
     <t>CBV-06</t>
   </si>
   <si>
-    <t>VW - 31.320 6X4/ 14M³ (TIK-1H96)</t>
-  </si>
-  <si>
     <t>CCV-01</t>
   </si>
   <si>
     <t>CAMINHAO COMBOIO VOLKSVAGEM</t>
   </si>
   <si>
-    <t>VW - DELIVERY 11.180 4X2 (TIG-2F86)</t>
-  </si>
-  <si>
     <t>CCV-02</t>
   </si>
   <si>
@@ -226,9 +205,6 @@
     <t>CAMINHÃO ESPARGIDOR ROMANELLI</t>
   </si>
   <si>
-    <t>EHR-600H -6.000 LITROS / VW-13.190 CRM 4X2 (OYP-9E01)</t>
-  </si>
-  <si>
     <t>2014/2014</t>
   </si>
   <si>
@@ -238,9 +214,6 @@
     <t>CAMINHÃO PRANCHA VOLKSWAGEN</t>
   </si>
   <si>
-    <t>26.260 - 6X2/CARREGA TUDO (2,60m X 8,50m)Carga: 8.820 kg/MUNCK Capacidade 20T (THV-6B08)</t>
-  </si>
-  <si>
     <t>2024/2025</t>
   </si>
   <si>
@@ -253,27 +226,15 @@
     <t>CAMINHAO PIPA VOLKSWAGEM</t>
   </si>
   <si>
-    <t>VW - 26.260 6X2 / 16.000 LITROS (THU-7J16)</t>
-  </si>
-  <si>
     <t>CPV-03</t>
   </si>
   <si>
-    <t>VW - 26.260 6X2 / 16.000 LITROS (TIM-2B16)</t>
-  </si>
-  <si>
     <t>CPV-04</t>
   </si>
   <si>
-    <t>VW - 26.260 6X2 / 16.000 LITROS (THO-4E30)</t>
-  </si>
-  <si>
     <t>CPV-05</t>
   </si>
   <si>
-    <t>VW - 26.260 6X2 / 16.000 LITROS (THZ-8D56)</t>
-  </si>
-  <si>
     <t>CSI-04</t>
   </si>
   <si>
@@ -334,9 +295,6 @@
     <t>CAVALO VOLKSWAGEM - 01</t>
   </si>
   <si>
-    <t>TRACTOR VW/29.530 MTM 6X4</t>
-  </si>
-  <si>
     <t>2023/2023</t>
   </si>
   <si>
@@ -358,27 +316,18 @@
     <t>VEÍCULO AUTOMOTOR COMPASS</t>
   </si>
   <si>
-    <t>JEEP LONGITUDE (SAN-3D29)</t>
-  </si>
-  <si>
     <t>VAG-01</t>
   </si>
   <si>
     <t xml:space="preserve">VEÍCULO AUTOMOTOR GOL </t>
   </si>
   <si>
-    <t>G5 5U7TA42 - 2022 - 1.0 (SBB-4B90)</t>
-  </si>
-  <si>
     <t>VAH-02</t>
   </si>
   <si>
     <t>VEÍCULO AUTOMOTOR HILUX</t>
   </si>
   <si>
-    <t>TOYOTA HILUX CDSRV (RID-5D47)</t>
-  </si>
-  <si>
     <t>2021/2021</t>
   </si>
   <si>
@@ -397,90 +346,51 @@
     <t>VEÍCULO AUTOMOTOR POLO</t>
   </si>
   <si>
-    <t>VW/POLO TRACK MA ROBUSTER (SAW-0A13)</t>
-  </si>
-  <si>
     <t>VAP-02</t>
   </si>
   <si>
-    <t>VW/POLO TRACK MA ROBUSTER (SAN-7B01)</t>
-  </si>
-  <si>
     <t>VAP-03</t>
   </si>
   <si>
-    <t>VW/POLO TRACK MA ROBUSTER (TIJ-2H42)</t>
-  </si>
-  <si>
     <t>VAP-04</t>
   </si>
   <si>
-    <t>VW/POLO TRACK MA ROBUSTER (UVE-4C25)</t>
-  </si>
-  <si>
     <t>VAP-05</t>
   </si>
   <si>
-    <t>VW/POLO TRACK MA ROBUSTER (UVD-9B45)</t>
-  </si>
-  <si>
     <t>VAS-01</t>
   </si>
   <si>
     <t>VEÍCULO AUTOMOTOR STRADA</t>
   </si>
   <si>
-    <t>FREEDOM CD 2023 - 1.3 (SBR-5J78)</t>
-  </si>
-  <si>
     <t>VAS-02</t>
   </si>
   <si>
-    <t>FREEDOM CD 2024 - 1.3 (SAP-0D29)</t>
-  </si>
-  <si>
     <t>VAS-03</t>
   </si>
   <si>
-    <t>FREEDOM CD 2024 - 1.3 (SAQ-5G44)</t>
-  </si>
-  <si>
     <t>2023/2024</t>
   </si>
   <si>
     <t>VAS-04</t>
   </si>
   <si>
-    <t>FREEDOM CS 2024 - 1.3 (SBF-4C03)</t>
-  </si>
-  <si>
     <t>VAS-05</t>
   </si>
   <si>
-    <t>FREEDOM CD 2026 - 1.3 (TIM-9B84)</t>
-  </si>
-  <si>
     <t>VAS-06</t>
   </si>
   <si>
-    <t>FREEDOM CD 2026 - 1.3 (RIG-0F05)</t>
-  </si>
-  <si>
     <t>VAS-07</t>
   </si>
   <si>
-    <t>FREEDOM CD 2027 - 1.3 (UUQ-3F25)</t>
-  </si>
-  <si>
     <t>VAT-01</t>
   </si>
   <si>
     <t>VEÍCULO AUTOMOTOR T-CROSS</t>
   </si>
   <si>
-    <t>VW/T CROSS SENSE TSI (SBD-1I38)</t>
-  </si>
-  <si>
     <t>VALOR TOTAL EM ATIVO</t>
   </si>
   <si>
@@ -497,12 +407,6 @@
   </si>
   <si>
     <t>VW/DELIVERY - 11.180 (UUN-2B64)</t>
-  </si>
-  <si>
-    <t>HAVAL H9 EXCLUSIVE TD480 (TIA-0A24)</t>
-  </si>
-  <si>
-    <t>HAVAL H9 EXCLUSIVE TD480 (THZ-4C14)</t>
   </si>
   <si>
     <t>VALOR IMPLEMNTOS C/ DEPRECIAÇÃO</t>
@@ -903,6 +807,57 @@
   </si>
   <si>
     <t>cars</t>
+  </si>
+  <si>
+    <t>CÓD FIPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VW - 31.320 6X4/ 14M³ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VW-13.190 CRM 4X2 </t>
+  </si>
+  <si>
+    <t>VW-26.260 - 6X2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VW - 26.260 6X2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VW-29.530 MTM 6X4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEEP LONGITUDE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOL G5 5U7TA42 - 1.0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOYOTA HILUX CDSRV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAVAL H9 EXCLUSIVE TD480 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VW/POLO TRACK MA ROBUSTER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREEDOM CD 2023 - 1.3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREEDOM CD 2024 - 1.3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREEDOM CS 2024 - 1.3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREEDOM CD 2026 - 1.3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREEDOM CD 2027 - 1.3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VW/T CROSS SENSE TSI </t>
   </si>
 </sst>
 </file>
@@ -1277,7 +1232,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1468,6 +1423,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2021,29 +1979,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66591557-DD37-43BD-B1BB-E5ED36EFCC0F}">
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="40" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.7109375" style="12" customWidth="1"/>
-    <col min="5" max="6" width="19" style="12" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="9" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="9" customWidth="1"/>
-    <col min="13" max="13" width="27.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="7" width="19" style="12" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" style="9" customWidth="1"/>
+    <col min="12" max="12" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="9" customWidth="1"/>
+    <col min="14" max="14" width="27.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="56" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="C1" s="57"/>
       <c r="D1" s="57"/>
@@ -2057,9 +2015,10 @@
       <c r="L1" s="57"/>
       <c r="M1" s="57"/>
       <c r="N1" s="57"/>
-      <c r="O1" s="58"/>
-    </row>
-    <row r="2" spans="1:19" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O1" s="57"/>
+      <c r="P1" s="58"/>
+    </row>
+    <row r="2" spans="1:20" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2070,40 +2029,43 @@
         <v>2</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="G2" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>124</v>
+      <c r="K2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="O2" s="22" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="P2" s="22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13"/>
       <c r="B3" s="23" t="s">
         <v>8</v>
@@ -2112,1903 +2074,1946 @@
         <v>9</v>
       </c>
       <c r="D3" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="11">
+      <c r="I3" s="11">
         <v>699276</v>
       </c>
-      <c r="I3" s="14">
+      <c r="J3" s="14">
         <f>580000</f>
         <v>580000</v>
       </c>
-      <c r="J3" s="14">
+      <c r="K3" s="14">
         <v>613394</v>
       </c>
-      <c r="K3" s="19">
+      <c r="L3" s="19">
         <v>45895</v>
       </c>
-      <c r="L3" s="20">
-        <f t="shared" ref="L3:L4" ca="1" si="0">IF(K3&lt;&gt;0,ROUND((K3-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-9.8333333333333342E-2</v>
-      </c>
-      <c r="M3" s="14">
+      <c r="M3" s="20">
+        <f t="shared" ref="M3:M4" ca="1" si="0">IF(L3&lt;&gt;0,ROUND((L3-TODAY())/30,1)*(10%/12),"-")</f>
+        <v>-9.9166666666666667E-2</v>
+      </c>
+      <c r="N3" s="14">
         <v>85000</v>
       </c>
-      <c r="N3" s="14">
-        <f ca="1">IF(L3&lt;&gt;"-",M3+M3*L3,0)</f>
-        <v>76641.666666666672</v>
-      </c>
-      <c r="O3" s="24">
-        <f t="shared" ref="O3:O43" ca="1" si="1">J3+IF(L3&lt;&gt;"-",N3,0)</f>
-        <v>690035.66666666663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O3" s="14">
+        <f ca="1">IF(M3&lt;&gt;"-",N3+N3*M3,0)</f>
+        <v>76570.833333333328</v>
+      </c>
+      <c r="P3" s="24">
+        <f t="shared" ref="P3:P43" ca="1" si="1">K3+IF(M3&lt;&gt;"-",O3,0)</f>
+        <v>689964.83333333337</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>13</v>
+        <v>225</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>254</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F4" s="11"/>
       <c r="G4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="11">
+        <v>222</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="11">
         <v>699277</v>
       </c>
-      <c r="I4" s="14">
-        <f t="shared" ref="I4:I8" si="2">580000</f>
+      <c r="J4" s="14">
+        <f t="shared" ref="J4:J8" si="2">580000</f>
         <v>580000</v>
       </c>
-      <c r="J4" s="14">
+      <c r="K4" s="14">
         <v>613394</v>
       </c>
-      <c r="K4" s="19">
+      <c r="L4" s="19">
         <v>45895</v>
       </c>
-      <c r="L4" s="20">
+      <c r="M4" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.8333333333333342E-2</v>
-      </c>
-      <c r="M4" s="14">
+        <v>-9.9166666666666667E-2</v>
+      </c>
+      <c r="N4" s="14">
         <v>85000</v>
       </c>
-      <c r="N4" s="14">
-        <f t="shared" ref="N4:N43" ca="1" si="3">IF(L4&lt;&gt;"-",M4+M4*L4,0)</f>
-        <v>76641.666666666672</v>
-      </c>
-      <c r="O4" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>690035.66666666663</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="14">
+        <f t="shared" ref="O4:O43" ca="1" si="3">IF(M4&lt;&gt;"-",N4+N4*M4,0)</f>
+        <v>76570.833333333328</v>
+      </c>
+      <c r="P4" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>689964.83333333337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13"/>
       <c r="B5" s="23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>254</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F5" s="11"/>
       <c r="G5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="11">
+        <v>222</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="11">
         <v>699278</v>
       </c>
-      <c r="I5" s="14">
+      <c r="J5" s="14">
         <f t="shared" si="2"/>
         <v>580000</v>
       </c>
-      <c r="J5" s="14">
+      <c r="K5" s="14">
         <v>613394</v>
       </c>
-      <c r="K5" s="19">
+      <c r="L5" s="19">
         <v>45895</v>
       </c>
-      <c r="L5" s="20">
-        <f ca="1">IF(K5&lt;&gt;0,ROUND((K5-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-9.8333333333333342E-2</v>
-      </c>
-      <c r="M5" s="14">
+      <c r="M5" s="20">
+        <f ca="1">IF(L5&lt;&gt;0,ROUND((L5-TODAY())/30,1)*(10%/12),"-")</f>
+        <v>-9.9166666666666667E-2</v>
+      </c>
+      <c r="N5" s="14">
         <v>85000</v>
       </c>
-      <c r="N5" s="14">
+      <c r="O5" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>76641.666666666672</v>
-      </c>
-      <c r="O5" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>690035.66666666663</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76570.833333333328</v>
+      </c>
+      <c r="P5" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>689964.83333333337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13"/>
       <c r="B6" s="23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>17</v>
+        <v>225</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>254</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F6" s="11"/>
       <c r="G6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="11">
+        <v>222</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="11">
         <v>699279</v>
       </c>
-      <c r="I6" s="14">
+      <c r="J6" s="14">
         <f t="shared" si="2"/>
         <v>580000</v>
       </c>
-      <c r="J6" s="14">
+      <c r="K6" s="14">
         <v>613394</v>
       </c>
-      <c r="K6" s="19">
+      <c r="L6" s="19">
         <v>45895</v>
       </c>
-      <c r="L6" s="20">
-        <f t="shared" ref="L6:L43" ca="1" si="4">IF(K6&lt;&gt;0,ROUND((K6-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-9.8333333333333342E-2</v>
-      </c>
-      <c r="M6" s="14">
+      <c r="M6" s="20">
+        <f t="shared" ref="M6:M43" ca="1" si="4">IF(L6&lt;&gt;0,ROUND((L6-TODAY())/30,1)*(10%/12),"-")</f>
+        <v>-9.9166666666666667E-2</v>
+      </c>
+      <c r="N6" s="14">
         <v>85000</v>
       </c>
-      <c r="N6" s="14">
+      <c r="O6" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>76641.666666666672</v>
-      </c>
-      <c r="O6" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>690035.66666666663</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76570.833333333328</v>
+      </c>
+      <c r="P6" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>689964.83333333337</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
       <c r="B7" s="23" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>19</v>
+        <v>225</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>254</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F7" s="11"/>
       <c r="G7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="11">
+        <v>222</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="11">
         <v>700155</v>
       </c>
-      <c r="I7" s="14">
+      <c r="J7" s="14">
         <f t="shared" si="2"/>
         <v>580000</v>
       </c>
-      <c r="J7" s="14">
+      <c r="K7" s="14">
         <v>613394</v>
       </c>
-      <c r="K7" s="19">
+      <c r="L7" s="19">
         <v>45895</v>
       </c>
-      <c r="L7" s="20">
+      <c r="M7" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-9.9166666666666667E-2</v>
+      </c>
+      <c r="N7" s="14">
+        <v>85000</v>
+      </c>
+      <c r="O7" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>76570.833333333328</v>
+      </c>
+      <c r="P7" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>689964.83333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="11">
+        <v>700155</v>
+      </c>
+      <c r="J8" s="14">
+        <f t="shared" si="2"/>
+        <v>580000</v>
+      </c>
+      <c r="K8" s="14">
+        <v>613394</v>
+      </c>
+      <c r="L8" s="19">
+        <v>45895</v>
+      </c>
+      <c r="M8" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-9.9166666666666667E-2</v>
+      </c>
+      <c r="N8" s="14">
+        <v>85000</v>
+      </c>
+      <c r="O8" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>76570.833333333328</v>
+      </c>
+      <c r="P8" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>689964.83333333337</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="11">
+        <v>700198</v>
+      </c>
+      <c r="J9" s="15">
+        <f>346000</f>
+        <v>346000</v>
+      </c>
+      <c r="K9" s="14">
+        <v>347599</v>
+      </c>
+      <c r="L9" s="19">
+        <v>45897</v>
+      </c>
+      <c r="M9" s="20">
         <f t="shared" ca="1" si="4"/>
         <v>-9.8333333333333342E-2</v>
       </c>
-      <c r="M7" s="14">
-        <v>85000</v>
-      </c>
-      <c r="N7" s="14">
+      <c r="N9" s="14">
+        <v>171014</v>
+      </c>
+      <c r="O9" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>76641.666666666672</v>
-      </c>
-      <c r="O7" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>690035.66666666663</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="23" t="s">
+        <v>154197.62333333332</v>
+      </c>
+      <c r="P9" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>501796.62333333329</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="E10" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H10" s="11">
+        <v>2026</v>
+      </c>
+      <c r="I10" s="11">
+        <v>726135</v>
+      </c>
+      <c r="J10" s="16">
+        <f>355000</f>
+        <v>355000</v>
+      </c>
+      <c r="K10" s="16">
+        <v>347599</v>
+      </c>
+      <c r="L10" s="19">
+        <v>46142</v>
+      </c>
+      <c r="M10" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-3.0833333333333334E-2</v>
+      </c>
+      <c r="N10" s="14">
+        <v>165000</v>
+      </c>
+      <c r="O10" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>159912.5</v>
+      </c>
+      <c r="P10" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>507511.5</v>
+      </c>
+      <c r="T10" s="17"/>
+    </row>
+    <row r="11" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="11">
-        <v>700155</v>
-      </c>
-      <c r="I8" s="14">
-        <f t="shared" si="2"/>
-        <v>580000</v>
-      </c>
-      <c r="J8" s="14">
-        <v>613394</v>
-      </c>
-      <c r="K8" s="19">
+      <c r="C11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="11">
+        <v>25464</v>
+      </c>
+      <c r="J11" s="14">
+        <f>190000+4497.24</f>
+        <v>194497.24</v>
+      </c>
+      <c r="K11" s="14">
+        <v>215885</v>
+      </c>
+      <c r="L11" s="19">
+        <v>45349</v>
+      </c>
+      <c r="M11" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.25083333333333335</v>
+      </c>
+      <c r="N11" s="14">
+        <v>282503.59000000003</v>
+      </c>
+      <c r="O11" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>211642.27284166668</v>
+      </c>
+      <c r="P11" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>427527.27284166671</v>
+      </c>
+      <c r="T11" s="17"/>
+    </row>
+    <row r="12" spans="1:20" s="12" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="14">
+        <f>560000+130000</f>
+        <v>690000</v>
+      </c>
+      <c r="K12" s="14">
+        <v>471760</v>
+      </c>
+      <c r="L12" s="19">
+        <v>45471</v>
+      </c>
+      <c r="M12" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.21666666666666667</v>
+      </c>
+      <c r="N12" s="16">
+        <f>130000+231500</f>
+        <v>361500</v>
+      </c>
+      <c r="O12" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>283175</v>
+      </c>
+      <c r="P12" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>754935</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="11">
+        <v>699282</v>
+      </c>
+      <c r="J13" s="14">
+        <f>495000</f>
+        <v>495000</v>
+      </c>
+      <c r="K13" s="14">
+        <v>494368</v>
+      </c>
+      <c r="L13" s="19">
         <v>45895</v>
       </c>
-      <c r="L8" s="20">
+      <c r="M13" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-9.9166666666666667E-2</v>
+      </c>
+      <c r="N13" s="14">
+        <v>115813</v>
+      </c>
+      <c r="O13" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>104328.21083333333</v>
+      </c>
+      <c r="P13" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>598696.21083333332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="11">
+        <v>699283</v>
+      </c>
+      <c r="J14" s="14">
+        <f t="shared" ref="J14:J16" si="5">495000</f>
+        <v>495000</v>
+      </c>
+      <c r="K14" s="14">
+        <v>494368</v>
+      </c>
+      <c r="L14" s="19">
+        <v>45895</v>
+      </c>
+      <c r="M14" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-9.9166666666666667E-2</v>
+      </c>
+      <c r="N14" s="14">
+        <v>115814</v>
+      </c>
+      <c r="O14" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>104329.11166666666</v>
+      </c>
+      <c r="P14" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>598697.11166666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="11">
+        <v>699825</v>
+      </c>
+      <c r="J15" s="14">
+        <f t="shared" si="5"/>
+        <v>495000</v>
+      </c>
+      <c r="K15" s="14">
+        <v>494368</v>
+      </c>
+      <c r="L15" s="19">
+        <v>45895</v>
+      </c>
+      <c r="M15" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-9.9166666666666667E-2</v>
+      </c>
+      <c r="N15" s="14">
+        <v>115815</v>
+      </c>
+      <c r="O15" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>104330.0125</v>
+      </c>
+      <c r="P15" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>598698.01249999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="11">
+        <v>700628</v>
+      </c>
+      <c r="J16" s="14">
+        <f t="shared" si="5"/>
+        <v>495000</v>
+      </c>
+      <c r="K16" s="14">
+        <v>494368</v>
+      </c>
+      <c r="L16" s="19">
+        <v>45895</v>
+      </c>
+      <c r="M16" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-9.9166666666666667E-2</v>
+      </c>
+      <c r="N16" s="14">
+        <v>115816</v>
+      </c>
+      <c r="O16" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>104330.91333333333</v>
+      </c>
+      <c r="P16" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>598698.91333333333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B17" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H17" s="11">
+        <v>2011</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J17" s="15">
+        <f>100000+10000+10000</f>
+        <v>120000</v>
+      </c>
+      <c r="K17" s="14">
+        <v>116088</v>
+      </c>
+      <c r="L17" s="19">
+        <v>44362</v>
+      </c>
+      <c r="M17" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.52500000000000002</v>
+      </c>
+      <c r="N17" s="14">
+        <v>50000</v>
+      </c>
+      <c r="O17" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>23750</v>
+      </c>
+      <c r="P17" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>139838</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J18" s="18">
+        <v>120000</v>
+      </c>
+      <c r="K18" s="14">
+        <v>90847</v>
+      </c>
+      <c r="L18" s="19">
+        <v>44362</v>
+      </c>
+      <c r="M18" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.52500000000000002</v>
+      </c>
+      <c r="N18" s="15">
+        <v>400000</v>
+      </c>
+      <c r="O18" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>190000</v>
+      </c>
+      <c r="P18" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>280847</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J19" s="18">
+        <v>200000</v>
+      </c>
+      <c r="K19" s="14">
+        <v>162893</v>
+      </c>
+      <c r="L19" s="19">
+        <v>44362</v>
+      </c>
+      <c r="M19" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.52500000000000002</v>
+      </c>
+      <c r="N19" s="15">
+        <v>250000</v>
+      </c>
+      <c r="O19" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>118750</v>
+      </c>
+      <c r="P19" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>281643</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J20" s="15">
+        <f>390000-61000-50000</f>
+        <v>279000</v>
+      </c>
+      <c r="K20" s="15">
+        <v>220524</v>
+      </c>
+      <c r="L20" s="19">
+        <v>44420</v>
+      </c>
+      <c r="M20" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.50916666666666666</v>
+      </c>
+      <c r="N20" s="15">
+        <f>61000+50000</f>
+        <v>111000</v>
+      </c>
+      <c r="O20" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>54482.5</v>
+      </c>
+      <c r="P20" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>275006.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H21" s="11">
+        <v>2025</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J21" s="18">
+        <f>415000+12000-75000</f>
+        <v>352000</v>
+      </c>
+      <c r="K21" s="14">
+        <v>338112</v>
+      </c>
+      <c r="L21" s="19">
+        <v>45712</v>
+      </c>
+      <c r="M21" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.15</v>
+      </c>
+      <c r="N21" s="15">
+        <v>75000</v>
+      </c>
+      <c r="O21" s="14">
+        <f t="shared" ca="1" si="3"/>
+        <v>63750</v>
+      </c>
+      <c r="P21" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>401862</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="65" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="11">
+        <v>700199</v>
+      </c>
+      <c r="J22" s="14">
+        <f>420000</f>
+        <v>420000</v>
+      </c>
+      <c r="K22" s="14">
+        <v>439697</v>
+      </c>
+      <c r="L22" s="19">
+        <v>45897</v>
+      </c>
+      <c r="M22" s="20">
         <f t="shared" ca="1" si="4"/>
         <v>-9.8333333333333342E-2</v>
       </c>
-      <c r="M8" s="14">
-        <v>85000</v>
-      </c>
-      <c r="N8" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>76641.666666666672</v>
-      </c>
-      <c r="O8" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>690035.66666666663</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="11">
-        <v>700198</v>
-      </c>
-      <c r="I9" s="15">
-        <f>346000</f>
-        <v>346000</v>
-      </c>
-      <c r="J9" s="14">
-        <v>347599</v>
-      </c>
-      <c r="K9" s="19">
-        <v>45897</v>
-      </c>
-      <c r="L9" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-9.8333333333333342E-2</v>
-      </c>
-      <c r="M9" s="14">
-        <v>171014</v>
-      </c>
-      <c r="N9" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>154197.62333333332</v>
-      </c>
-      <c r="O9" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>501796.62333333329</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G10" s="11">
-        <v>2026</v>
-      </c>
-      <c r="H10" s="11">
-        <v>726135</v>
-      </c>
-      <c r="I10" s="16">
-        <f>355000</f>
-        <v>355000</v>
-      </c>
-      <c r="J10" s="16">
-        <v>347599</v>
-      </c>
-      <c r="K10" s="19">
-        <v>46142</v>
-      </c>
-      <c r="L10" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-0.03</v>
-      </c>
-      <c r="M10" s="14">
-        <v>165000</v>
-      </c>
-      <c r="N10" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>160050</v>
-      </c>
-      <c r="O10" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>507649</v>
-      </c>
-      <c r="S10" s="17"/>
-    </row>
-    <row r="11" spans="1:19" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="11">
-        <v>25464</v>
-      </c>
-      <c r="I11" s="14">
-        <f>190000+4497.24</f>
-        <v>194497.24</v>
-      </c>
-      <c r="J11" s="14">
-        <v>215885</v>
-      </c>
-      <c r="K11" s="19">
-        <v>45349</v>
-      </c>
-      <c r="L11" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-0.25</v>
-      </c>
-      <c r="M11" s="14">
-        <v>282503.59000000003</v>
-      </c>
-      <c r="N11" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>211877.6925</v>
-      </c>
-      <c r="O11" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>427762.6925</v>
-      </c>
-      <c r="S11" s="17"/>
-    </row>
-    <row r="12" spans="1:19" s="12" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" s="14">
-        <f>560000+130000</f>
-        <v>690000</v>
-      </c>
-      <c r="J12" s="14">
-        <v>471760</v>
-      </c>
-      <c r="K12" s="19">
-        <v>45471</v>
-      </c>
-      <c r="L12" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-0.21666666666666667</v>
-      </c>
-      <c r="M12" s="16">
-        <f>130000+231500</f>
-        <v>361500</v>
-      </c>
-      <c r="N12" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>283175</v>
-      </c>
-      <c r="O12" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>754935</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="11">
-        <v>699282</v>
-      </c>
-      <c r="I13" s="14">
-        <f>495000</f>
-        <v>495000</v>
-      </c>
-      <c r="J13" s="14">
-        <v>494368</v>
-      </c>
-      <c r="K13" s="19">
-        <v>45895</v>
-      </c>
-      <c r="L13" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-9.8333333333333342E-2</v>
-      </c>
-      <c r="M13" s="14">
-        <v>115813</v>
-      </c>
-      <c r="N13" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>104424.72166666666</v>
-      </c>
-      <c r="O13" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>598792.72166666668</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="11">
-        <v>699283</v>
-      </c>
-      <c r="I14" s="14">
-        <f t="shared" ref="I14:I16" si="5">495000</f>
-        <v>495000</v>
-      </c>
-      <c r="J14" s="14">
-        <v>494368</v>
-      </c>
-      <c r="K14" s="19">
-        <v>45895</v>
-      </c>
-      <c r="L14" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-9.8333333333333342E-2</v>
-      </c>
-      <c r="M14" s="14">
-        <v>115814</v>
-      </c>
-      <c r="N14" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>104425.62333333334</v>
-      </c>
-      <c r="O14" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>598793.62333333329</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="11">
-        <v>699825</v>
-      </c>
-      <c r="I15" s="14">
-        <f t="shared" si="5"/>
-        <v>495000</v>
-      </c>
-      <c r="J15" s="14">
-        <v>494368</v>
-      </c>
-      <c r="K15" s="19">
-        <v>45895</v>
-      </c>
-      <c r="L15" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-9.8333333333333342E-2</v>
-      </c>
-      <c r="M15" s="14">
-        <v>115815</v>
-      </c>
-      <c r="N15" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>104426.52499999999</v>
-      </c>
-      <c r="O15" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>598794.52500000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="11">
-        <v>700628</v>
-      </c>
-      <c r="I16" s="14">
-        <f t="shared" si="5"/>
-        <v>495000</v>
-      </c>
-      <c r="J16" s="14">
-        <v>494368</v>
-      </c>
-      <c r="K16" s="19">
-        <v>45895</v>
-      </c>
-      <c r="L16" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-9.8333333333333342E-2</v>
-      </c>
-      <c r="M16" s="14">
-        <v>115816</v>
-      </c>
-      <c r="N16" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>104427.42666666667</v>
-      </c>
-      <c r="O16" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>598795.42666666664</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B17" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G17" s="11">
-        <v>2011</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I17" s="15">
-        <f>100000+10000+10000</f>
-        <v>120000</v>
-      </c>
-      <c r="J17" s="14">
-        <v>116088</v>
-      </c>
-      <c r="K17" s="19">
-        <v>44362</v>
-      </c>
-      <c r="L17" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-0.52416666666666667</v>
-      </c>
-      <c r="M17" s="14">
-        <v>50000</v>
-      </c>
-      <c r="N17" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>23791.666666666668</v>
-      </c>
-      <c r="O17" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>139879.66666666666</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" s="18">
-        <v>120000</v>
-      </c>
-      <c r="J18" s="14">
-        <v>90847</v>
-      </c>
-      <c r="K18" s="19">
-        <v>44362</v>
-      </c>
-      <c r="L18" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-0.52416666666666667</v>
-      </c>
-      <c r="M18" s="15">
-        <v>400000</v>
-      </c>
-      <c r="N18" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>190333.33333333334</v>
-      </c>
-      <c r="O18" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>281180.33333333337</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I19" s="18">
-        <v>200000</v>
-      </c>
-      <c r="J19" s="14">
-        <v>162893</v>
-      </c>
-      <c r="K19" s="19">
-        <v>44362</v>
-      </c>
-      <c r="L19" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-0.52416666666666667</v>
-      </c>
-      <c r="M19" s="15">
-        <v>250000</v>
-      </c>
-      <c r="N19" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>118958.33333333333</v>
-      </c>
-      <c r="O19" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>281851.33333333331</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I20" s="15">
-        <f>390000-61000-50000</f>
-        <v>279000</v>
-      </c>
-      <c r="J20" s="15">
-        <v>220524</v>
-      </c>
-      <c r="K20" s="19">
-        <v>44420</v>
-      </c>
-      <c r="L20" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-0.5083333333333333</v>
-      </c>
-      <c r="M20" s="15">
-        <f>61000+50000</f>
-        <v>111000</v>
-      </c>
-      <c r="N20" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>54575</v>
-      </c>
-      <c r="O20" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>275099</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G21" s="11">
-        <v>2025</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I21" s="18">
-        <f>415000+12000-75000</f>
-        <v>352000</v>
-      </c>
-      <c r="J21" s="14">
-        <v>338112</v>
-      </c>
-      <c r="K21" s="19">
-        <v>45712</v>
-      </c>
-      <c r="L21" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-0.14916666666666664</v>
-      </c>
-      <c r="M21" s="15">
-        <v>75000</v>
-      </c>
-      <c r="N21" s="14">
-        <f t="shared" ca="1" si="3"/>
-        <v>63812.5</v>
-      </c>
-      <c r="O21" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>401924.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="11">
-        <v>700199</v>
-      </c>
-      <c r="I22" s="14">
-        <f>420000</f>
-        <v>420000</v>
-      </c>
-      <c r="J22" s="14">
-        <v>439697</v>
-      </c>
-      <c r="K22" s="19">
-        <v>45897</v>
-      </c>
-      <c r="L22" s="20">
-        <f t="shared" ca="1" si="4"/>
-        <v>-9.8333333333333342E-2</v>
-      </c>
-      <c r="M22" s="15">
+      <c r="N22" s="15">
         <v>730000</v>
       </c>
-      <c r="N22" s="14">
+      <c r="O22" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>658216.66666666663</v>
       </c>
-      <c r="O22" s="24">
+      <c r="P22" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>1097913.6666666665</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="23" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="D23" s="65" t="s">
+        <v>90</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G23" s="11">
+        <v>215</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H23" s="11">
         <v>2026</v>
       </c>
-      <c r="H23" s="11">
+      <c r="I23" s="11">
         <v>726136</v>
       </c>
-      <c r="I23" s="16">
+      <c r="J23" s="16">
         <f>355000+35000*24.35%</f>
         <v>363522.5</v>
       </c>
-      <c r="J23" s="16">
+      <c r="K23" s="16">
         <v>359752</v>
       </c>
-      <c r="K23" s="19">
+      <c r="L23" s="19">
         <v>44362</v>
       </c>
-      <c r="L23" s="20">
+      <c r="M23" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.52416666666666667</v>
-      </c>
-      <c r="M23" s="15">
+        <v>-0.52500000000000002</v>
+      </c>
+      <c r="N23" s="15">
         <v>350000</v>
       </c>
-      <c r="N23" s="14">
+      <c r="O23" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>166541.66666666666</v>
-      </c>
-      <c r="O23" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>526293.66666666663</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>166250</v>
+      </c>
+      <c r="P23" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>526002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="23" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="11"/>
+        <v>48</v>
+      </c>
+      <c r="D24" s="65"/>
       <c r="E24" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I24" s="15">
+      <c r="J24" s="15">
         <v>315000</v>
       </c>
-      <c r="J24" s="15">
+      <c r="K24" s="15">
         <v>305453</v>
       </c>
-      <c r="K24" s="19">
+      <c r="L24" s="19">
         <v>46235</v>
       </c>
-      <c r="L24" s="20">
+      <c r="M24" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>-4.1666666666666666E-3</v>
-      </c>
-      <c r="M24" s="15">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+      <c r="N24" s="15">
         <v>200000</v>
       </c>
-      <c r="N24" s="14">
+      <c r="O24" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>199166.66666666666</v>
-      </c>
-      <c r="O24" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>504619.66666666663</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>199000</v>
+      </c>
+      <c r="P24" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>504453</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="23" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>66</v>
+        <v>229</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G25" s="11">
+        <v>215</v>
+      </c>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H25" s="11">
         <v>2026</v>
       </c>
-      <c r="H25" s="11">
+      <c r="I25" s="11">
         <v>726215</v>
       </c>
-      <c r="I25" s="16">
+      <c r="J25" s="16">
         <f>748000+35000*51.3%</f>
         <v>765955</v>
       </c>
-      <c r="J25" s="16">
+      <c r="K25" s="16">
         <v>703009</v>
       </c>
-      <c r="K25" s="19">
+      <c r="L25" s="19">
         <v>46142</v>
       </c>
-      <c r="L25" s="20">
+      <c r="M25" s="20">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.03</v>
-      </c>
-      <c r="M25" s="14">
+        <v>-3.0833333333333334E-2</v>
+      </c>
+      <c r="N25" s="14">
         <f>196000+262000</f>
         <v>458000</v>
       </c>
-      <c r="N25" s="14">
+      <c r="O25" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>444260</v>
-      </c>
-      <c r="O25" s="24">
-        <f t="shared" ca="1" si="1"/>
-        <v>1147269</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>443878.33333333331</v>
+      </c>
+      <c r="P25" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>1146887.3333333333</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="25" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="F26" s="11"/>
       <c r="G26" s="11" t="s">
-        <v>67</v>
+        <v>223</v>
       </c>
       <c r="H26" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I26" s="14">
+      <c r="J26" s="14">
         <v>153000</v>
       </c>
-      <c r="J26" s="14">
+      <c r="K26" s="14">
         <v>144999</v>
       </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="20" t="str">
+      <c r="L26" s="11"/>
+      <c r="M26" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14">
+      <c r="N26" s="14"/>
+      <c r="O26" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O26" s="24">
+      <c r="P26" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>144999</v>
       </c>
     </row>
-    <row r="27" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="23" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F27" s="11"/>
       <c r="G27" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" s="11">
+        <v>223</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I27" s="11">
         <v>60901</v>
       </c>
-      <c r="I27" s="14">
+      <c r="J27" s="14">
         <v>62990</v>
       </c>
-      <c r="J27" s="14">
+      <c r="K27" s="14">
         <v>51770</v>
       </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="20" t="str">
+      <c r="L27" s="11"/>
+      <c r="M27" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14">
+      <c r="N27" s="14"/>
+      <c r="O27" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O27" s="24">
+      <c r="P27" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>51770</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="23" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>80</v>
+        <v>232</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="F28" s="11"/>
       <c r="G28" s="11" t="s">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="H28" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="I28" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I28" s="15">
+      <c r="J28" s="15">
         <f>48*4825</f>
         <v>231600</v>
       </c>
-      <c r="J28" s="15">
+      <c r="K28" s="15">
         <v>204280</v>
       </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="20" t="str">
+      <c r="L28" s="11"/>
+      <c r="M28" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15">
+      <c r="N28" s="15"/>
+      <c r="O28" s="15">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O28" s="26">
+      <c r="P28" s="26">
         <f t="shared" ca="1" si="1"/>
         <v>204280</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="23" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>121</v>
+        <v>233</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="F29" s="11"/>
       <c r="G29" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="11">
+        <v>223</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="11">
         <v>109879</v>
       </c>
-      <c r="I29" s="15">
+      <c r="J29" s="15">
         <v>312550</v>
       </c>
-      <c r="J29" s="14">
+      <c r="K29" s="14">
         <v>303295</v>
       </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="20" t="str">
+      <c r="L29" s="11"/>
+      <c r="M29" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M29" s="15"/>
-      <c r="N29" s="14">
+      <c r="N29" s="15"/>
+      <c r="O29" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O29" s="24">
+      <c r="P29" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>303295</v>
       </c>
     </row>
-    <row r="30" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
       <c r="B30" s="23" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>122</v>
+        <v>233</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="F30" s="11"/>
       <c r="G30" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="11">
+        <v>223</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" s="11">
         <v>109886</v>
       </c>
-      <c r="I30" s="15">
+      <c r="J30" s="15">
         <v>312550</v>
       </c>
-      <c r="J30" s="14">
+      <c r="K30" s="14">
         <v>303295</v>
       </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="20" t="str">
+      <c r="L30" s="11"/>
+      <c r="M30" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M30" s="15"/>
-      <c r="N30" s="14">
+      <c r="N30" s="15"/>
+      <c r="O30" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O30" s="24">
+      <c r="P30" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>303295</v>
       </c>
     </row>
-    <row r="31" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13"/>
       <c r="B31" s="23" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>87</v>
+        <v>234</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F31" s="11"/>
       <c r="G31" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H31" s="11">
+        <v>223</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" s="11">
         <v>672185</v>
       </c>
-      <c r="I31" s="14">
+      <c r="J31" s="14">
         <v>77256.5</v>
       </c>
-      <c r="J31" s="14">
+      <c r="K31" s="14">
         <v>75643</v>
       </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="20" t="str">
+      <c r="L31" s="11"/>
+      <c r="M31" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14">
+      <c r="N31" s="14"/>
+      <c r="O31" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O31" s="24">
+      <c r="P31" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>75643</v>
       </c>
     </row>
-    <row r="32" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>
       <c r="B32" s="23" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>89</v>
+        <v>234</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F32" s="11"/>
       <c r="G32" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H32" s="11">
+        <v>223</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I32" s="11">
         <v>736645</v>
       </c>
-      <c r="I32" s="14">
+      <c r="J32" s="14">
         <v>78867.61</v>
       </c>
-      <c r="J32" s="14">
+      <c r="K32" s="14">
         <v>75643</v>
       </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="20" t="str">
+      <c r="L32" s="11"/>
+      <c r="M32" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M32" s="15"/>
-      <c r="N32" s="14">
+      <c r="N32" s="15"/>
+      <c r="O32" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O32" s="24">
+      <c r="P32" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>75643</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="23" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>91</v>
+        <v>234</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F33" s="11"/>
       <c r="G33" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H33" s="11">
+        <v>223</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I33" s="11">
         <v>775452</v>
       </c>
-      <c r="I33" s="14">
+      <c r="J33" s="14">
         <v>82186.509999999995</v>
       </c>
-      <c r="J33" s="14">
+      <c r="K33" s="14">
         <v>75643</v>
       </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="20" t="str">
+      <c r="L33" s="11"/>
+      <c r="M33" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14">
+      <c r="N33" s="14"/>
+      <c r="O33" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O33" s="24">
+      <c r="P33" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>75643</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
       <c r="B34" s="23" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>93</v>
+        <v>234</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F34" s="11"/>
       <c r="G34" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H34" s="5">
+        <v>223</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I34" s="5">
         <v>961871</v>
       </c>
-      <c r="I34" s="16">
+      <c r="J34" s="16">
         <v>82143.600000000006</v>
       </c>
-      <c r="J34" s="16">
+      <c r="K34" s="16">
         <v>81531</v>
       </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="20" t="str">
+      <c r="L34" s="11"/>
+      <c r="M34" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M34" s="15"/>
-      <c r="N34" s="14">
+      <c r="N34" s="15"/>
+      <c r="O34" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O34" s="24">
+      <c r="P34" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>81531</v>
       </c>
     </row>
-    <row r="35" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="23" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>95</v>
+        <v>234</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F35" s="11"/>
       <c r="G35" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H35" s="5">
+        <v>223</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I35" s="5">
         <v>961872</v>
       </c>
-      <c r="I35" s="16">
+      <c r="J35" s="16">
         <v>82143.600000000006</v>
       </c>
-      <c r="J35" s="16">
+      <c r="K35" s="16">
         <v>81531</v>
       </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="20" t="str">
+      <c r="L35" s="11"/>
+      <c r="M35" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M35" s="15"/>
-      <c r="N35" s="14">
+      <c r="N35" s="15"/>
+      <c r="O35" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O35" s="24">
+      <c r="P35" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>81531</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="23" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="G36" s="11">
+        <v>220</v>
+      </c>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="H36" s="11">
         <v>2023</v>
       </c>
-      <c r="H36" s="11">
+      <c r="I36" s="11">
         <v>6242232</v>
       </c>
-      <c r="I36" s="14">
+      <c r="J36" s="14">
         <v>101681.98</v>
       </c>
-      <c r="J36" s="14">
+      <c r="K36" s="14">
         <v>81644</v>
       </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="20" t="str">
+      <c r="L36" s="11"/>
+      <c r="M36" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14">
+      <c r="N36" s="14"/>
+      <c r="O36" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O36" s="24">
+      <c r="P36" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>81644</v>
       </c>
     </row>
-    <row r="37" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="23" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>100</v>
+        <v>236</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="G37" s="11">
+        <v>220</v>
+      </c>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="H37" s="11">
         <v>2023</v>
       </c>
-      <c r="H37" s="11">
+      <c r="I37" s="11">
         <v>6411826</v>
       </c>
-      <c r="I37" s="14">
+      <c r="J37" s="14">
         <v>102992.29</v>
       </c>
-      <c r="J37" s="14">
+      <c r="K37" s="14">
         <v>89461</v>
       </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="20" t="str">
+      <c r="L37" s="11"/>
+      <c r="M37" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14">
+      <c r="N37" s="14"/>
+      <c r="O37" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O37" s="24">
+      <c r="P37" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>89461</v>
       </c>
     </row>
-    <row r="38" spans="1:15" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="23" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>102</v>
+        <v>236</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="F38" s="11"/>
       <c r="G38" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="H38" s="11">
+        <v>223</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I38" s="11">
         <v>6541809</v>
       </c>
-      <c r="I38" s="14">
+      <c r="J38" s="14">
         <v>98022.77</v>
       </c>
-      <c r="J38" s="14">
+      <c r="K38" s="14">
         <v>89461</v>
       </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="20" t="str">
+      <c r="L38" s="11"/>
+      <c r="M38" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14">
+      <c r="N38" s="14"/>
+      <c r="O38" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O38" s="24">
+      <c r="P38" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>89461</v>
       </c>
     </row>
-    <row r="39" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="23" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>105</v>
+        <v>237</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="F39" s="11"/>
       <c r="G39" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="11">
+        <v>223</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="11">
         <v>6872066</v>
       </c>
-      <c r="I39" s="14">
+      <c r="J39" s="14">
         <v>89584</v>
       </c>
-      <c r="J39" s="14">
+      <c r="K39" s="14">
         <v>92039</v>
       </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="20" t="str">
+      <c r="L39" s="11"/>
+      <c r="M39" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14">
+      <c r="N39" s="14"/>
+      <c r="O39" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O39" s="24">
+      <c r="P39" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>92039</v>
       </c>
     </row>
-    <row r="40" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="23" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="F40" s="11"/>
       <c r="G40" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H40" s="11">
+        <v>223</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I40" s="11">
         <v>8238773</v>
       </c>
-      <c r="I40" s="14">
+      <c r="J40" s="14">
         <v>113270.39999999999</v>
       </c>
-      <c r="J40" s="14">
+      <c r="K40" s="14">
         <v>98703</v>
       </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="20" t="str">
+      <c r="L40" s="11"/>
+      <c r="M40" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14">
+      <c r="N40" s="14"/>
+      <c r="O40" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O40" s="24">
+      <c r="P40" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>98703</v>
       </c>
     </row>
-    <row r="41" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="23" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>255</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="F41" s="11"/>
       <c r="G41" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H41" s="11">
+        <v>223</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I41" s="11">
         <v>8440887</v>
       </c>
-      <c r="I41" s="14">
+      <c r="J41" s="14">
         <v>113932.8</v>
       </c>
-      <c r="J41" s="14">
+      <c r="K41" s="14">
         <v>98703</v>
       </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="20" t="str">
+      <c r="L41" s="11"/>
+      <c r="M41" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14">
+      <c r="N41" s="14"/>
+      <c r="O41" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O41" s="24">
+      <c r="P41" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>98703</v>
       </c>
     </row>
-    <row r="42" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="25" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>111</v>
+        <v>239</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H42" s="5">
+        <v>220</v>
+      </c>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I42" s="5">
         <v>8583644</v>
       </c>
-      <c r="I42" s="15">
+      <c r="J42" s="15">
         <v>112156.32</v>
       </c>
-      <c r="J42" s="15">
+      <c r="K42" s="15">
         <v>111062</v>
       </c>
-      <c r="K42" s="5"/>
-      <c r="L42" s="20" t="str">
+      <c r="L42" s="5"/>
+      <c r="M42" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M42" s="15"/>
-      <c r="N42" s="14">
+      <c r="N42" s="15"/>
+      <c r="O42" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O42" s="24">
+      <c r="P42" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>111062</v>
       </c>
     </row>
-    <row r="43" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="23" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>114</v>
+        <v>240</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="G43" s="11">
+        <v>215</v>
+      </c>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="H43" s="11">
         <v>2023</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="I43" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I43" s="14">
+      <c r="J43" s="14">
         <v>94000</v>
       </c>
-      <c r="J43" s="14">
+      <c r="K43" s="14">
         <v>94771</v>
       </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="20" t="str">
+      <c r="L43" s="11"/>
+      <c r="M43" s="20" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>-</v>
       </c>
-      <c r="M43" s="14"/>
-      <c r="N43" s="14">
+      <c r="N43" s="14"/>
+      <c r="O43" s="14">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="O43" s="24">
+      <c r="P43" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>94771</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="59" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="C44" s="60"/>
       <c r="D44" s="60"/>
@@ -4016,52 +4021,55 @@
       <c r="F44" s="60"/>
       <c r="G44" s="60"/>
       <c r="H44" s="60"/>
-      <c r="I44" s="27">
-        <f>SUM(I3:I43)</f>
-        <v>12281903.119999999</v>
-      </c>
+      <c r="I44" s="60"/>
       <c r="J44" s="27">
         <f>SUM(J3:J43)</f>
+        <v>12281903.119999999</v>
+      </c>
+      <c r="K44" s="27">
+        <f>SUM(K3:K43)</f>
         <v>11930528</v>
       </c>
-      <c r="K44" s="27"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="29">
-        <f>SUM(M3:M43)</f>
+      <c r="L44" s="27"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="29">
+        <f>SUM(N3:N43)</f>
         <v>4577275.59</v>
       </c>
-      <c r="N44" s="29">
-        <f ca="1">SUM(N3:N43)</f>
-        <v>3606510.4458333328</v>
-      </c>
-      <c r="O44" s="30">
+      <c r="O44" s="29">
         <f ca="1">SUM(O3:O43)</f>
-        <v>15537038.445833331</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3603748.1445083329</v>
+      </c>
+      <c r="P44" s="30">
+        <f ca="1">SUM(P3:P43)</f>
+        <v>15534276.144508334</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
-      <c r="G45" s="6"/>
+      <c r="G45" s="21"/>
       <c r="H45" s="6"/>
-      <c r="I45" s="7"/>
+      <c r="I45" s="6"/>
       <c r="J45" s="7"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="8"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:M2" xr:uid="{6B458174-F3E0-4412-A327-9FB759D162B1}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:M90">
+  <autoFilter ref="B2:N2" xr:uid="{6B458174-F3E0-4412-A327-9FB759D162B1}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:N90">
       <sortCondition ref="B2"/>
     </sortState>
   </autoFilter>
   <mergeCells count="2">
-    <mergeCell ref="B1:O1"/>
-    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="B44:I44"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="55" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -4087,7 +4095,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="61" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C1" s="62"/>
       <c r="D1" s="62"/>
@@ -4117,22 +4125,22 @@
         <v>5</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="32" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="E3" s="32">
         <v>2023</v>
@@ -4148,19 +4156,19 @@
       </c>
       <c r="I3" s="55">
         <f ca="1">IF(H3&lt;&gt;0,ROUND((H3-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.23249999999999998</v>
+        <v>-0.23333333333333334</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="31"/>
       <c r="B4" s="32" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="E4" s="32">
         <v>2023</v>
@@ -4176,18 +4184,18 @@
       </c>
       <c r="I4" s="55">
         <f t="shared" ref="I4:I8" ca="1" si="0">IF(H4&lt;&gt;0,ROUND((H4-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.23249999999999998</v>
+        <v>-0.23333333333333334</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="E5" s="32">
         <v>2023</v>
@@ -4203,18 +4211,18 @@
       </c>
       <c r="I5" s="55">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.23249999999999998</v>
+        <v>-0.23333333333333334</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="32" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="E6" s="32">
         <v>2023</v>
@@ -4230,18 +4238,18 @@
       </c>
       <c r="I6" s="55">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.23249999999999998</v>
+        <v>-0.23333333333333334</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="E7" s="32">
         <v>2023</v>
@@ -4257,18 +4265,18 @@
       </c>
       <c r="I7" s="55">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.23249999999999998</v>
+        <v>-0.23333333333333334</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="32" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="E8" s="32">
         <v>2022</v>
@@ -4284,18 +4292,18 @@
       </c>
       <c r="I8" s="55">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.38833333333333336</v>
+        <v>-0.38916666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="32" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="E9" s="32">
         <v>2022</v>
@@ -4311,19 +4319,19 @@
       </c>
       <c r="I9" s="55">
         <f ca="1">IF(H9&lt;&gt;0,ROUND((H9-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.38833333333333336</v>
+        <v>-0.38916666666666666</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="31"/>
       <c r="B10" s="35" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="E10" s="32">
         <v>2022</v>
@@ -4339,19 +4347,19 @@
       </c>
       <c r="I10" s="55">
         <f t="shared" ref="I10:I32" ca="1" si="1">IF(H10&lt;&gt;0,ROUND((H10-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.40583333333333332</v>
+        <v>-0.40666666666666662</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="31"/>
       <c r="B11" s="32" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="E11" s="32">
         <v>2026</v>
@@ -4368,19 +4376,19 @@
       </c>
       <c r="I11" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-6.3333333333333325E-2</v>
+        <v>-6.4166666666666664E-2</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="31"/>
       <c r="B12" s="32" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="E12" s="32">
         <v>2026</v>
@@ -4397,16 +4405,16 @@
       </c>
       <c r="I12" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-6.3333333333333325E-2</v>
+        <v>-6.4166666666666664E-2</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="31"/>
       <c r="B13" s="32" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="D13" s="35"/>
       <c r="E13" s="35"/>
@@ -4423,13 +4431,13 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="31"/>
       <c r="B14" s="32" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E14" s="32">
         <v>2024</v>
@@ -4450,13 +4458,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="32" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E15" s="32">
         <v>2024</v>
@@ -4472,18 +4480,18 @@
       </c>
       <c r="I15" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-8.2500000000000004E-2</v>
+        <v>-8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="32" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E16" s="32">
         <v>2024</v>
@@ -4499,18 +4507,18 @@
       </c>
       <c r="I16" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-8.2500000000000004E-2</v>
+        <v>-8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B17" s="32" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E17" s="32">
         <v>2025</v>
@@ -4526,18 +4534,18 @@
       </c>
       <c r="I17" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-7.0833333333333331E-2</v>
+        <v>-7.1666666666666656E-2</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B18" s="32" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E18" s="32">
         <v>2026</v>
@@ -4558,13 +4566,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" s="32" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E19" s="32">
         <v>2026</v>
@@ -4580,18 +4588,18 @@
       </c>
       <c r="I19" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-8.3333333333333332E-3</v>
+        <v>-9.1666666666666667E-3</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B20" s="32" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E20" s="32">
         <v>2026</v>
@@ -4607,18 +4615,18 @@
       </c>
       <c r="I20" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-8.3333333333333332E-3</v>
+        <v>-9.1666666666666667E-3</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21" s="32" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="E21" s="32">
         <v>2023</v>
@@ -4635,18 +4643,18 @@
       </c>
       <c r="I21" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.20666666666666667</v>
+        <v>-0.20749999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B22" s="32" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E22" s="32">
         <v>2024</v>
@@ -4667,13 +4675,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23" s="32" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E23" s="32">
         <v>2024</v>
@@ -4689,18 +4697,18 @@
       </c>
       <c r="I23" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-8.2500000000000004E-2</v>
+        <v>-8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B24" s="32" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E24" s="32">
         <v>2025</v>
@@ -4716,18 +4724,18 @@
       </c>
       <c r="I24" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-8.2500000000000004E-2</v>
+        <v>-8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" s="32" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E25" s="32">
         <v>2025</v>
@@ -4743,18 +4751,18 @@
       </c>
       <c r="I25" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-7.0833333333333331E-2</v>
+        <v>-7.1666666666666656E-2</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B26" s="32" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E26" s="32">
         <v>2025</v>
@@ -4770,18 +4778,18 @@
       </c>
       <c r="I26" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-8.3333333333333332E-3</v>
+        <v>-9.1666666666666667E-3</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B27" s="32" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E27" s="32">
         <v>2025</v>
@@ -4797,22 +4805,22 @@
       </c>
       <c r="I27" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-8.3333333333333332E-3</v>
+        <v>-9.1666666666666667E-3</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="31"/>
       <c r="B28" s="32" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="E28" s="32" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="F28" s="32">
         <v>25465</v>
@@ -4826,19 +4834,19 @@
       </c>
       <c r="I28" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.23583333333333334</v>
+        <v>-0.23666666666666666</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="31"/>
       <c r="B29" s="32" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="E29" s="32">
         <v>2022</v>
@@ -4854,19 +4862,19 @@
       </c>
       <c r="I29" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.43416666666666665</v>
+        <v>-0.435</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="31"/>
       <c r="B30" s="32" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="D30" s="32" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="E30" s="32">
         <v>2022</v>
@@ -4888,13 +4896,13 @@
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="31"/>
       <c r="B31" s="32" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="D31" s="32" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="E31" s="32">
         <v>2025</v>
@@ -4910,19 +4918,19 @@
       </c>
       <c r="I31" s="55">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.12333333333333334</v>
+        <v>-0.12416666666666666</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="31"/>
       <c r="B32" s="33" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="E32" s="32">
         <v>2025</v>
@@ -4944,13 +4952,13 @@
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="31"/>
       <c r="B33" s="33" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="E33" s="33">
         <v>2026</v>
@@ -4972,16 +4980,16 @@
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="31"/>
       <c r="B34" s="32" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="E34" s="32" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="F34" s="32">
         <v>3315</v>
@@ -5000,16 +5008,16 @@
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="31"/>
       <c r="B35" s="33" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="E35" s="32" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="F35" s="32">
         <v>2945</v>
@@ -5028,16 +5036,16 @@
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="31"/>
       <c r="B36" s="32" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="E36" s="32" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F36" s="32">
         <v>6151</v>
@@ -5050,22 +5058,22 @@
       </c>
       <c r="I36" s="55">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.12583333333333332</v>
+        <v>-0.12666666666666665</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="31"/>
       <c r="B37" s="32" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="E37" s="32" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F37" s="32">
         <v>1304</v>
@@ -5078,22 +5086,22 @@
       </c>
       <c r="I37" s="55">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.12583333333333332</v>
+        <v>-0.12666666666666665</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="44"/>
       <c r="B38" s="33" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F38" s="33">
         <v>1435</v>
@@ -5111,13 +5119,13 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B39" s="32" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="E39" s="32" t="s">
         <v>6</v>
@@ -5134,18 +5142,18 @@
       </c>
       <c r="I39" s="55">
         <f ca="1">IF(H39&lt;&gt;0,ROUND((H39-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.23833333333333334</v>
+        <v>-0.23916666666666667</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="33" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="D40" s="33" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="E40" s="33">
         <v>2022</v>
@@ -5162,18 +5170,18 @@
       </c>
       <c r="I40" s="55">
         <f t="shared" ref="I40:I43" ca="1" si="3">IF(H40&lt;&gt;0,ROUND((H40-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.41916666666666663</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B41" s="32" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="E41" s="32">
         <v>2023</v>
@@ -5189,19 +5197,19 @@
       </c>
       <c r="I41" s="55">
         <f t="shared" ca="1" si="3"/>
-        <v>-0.26666666666666666</v>
+        <v>-0.26750000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="31"/>
       <c r="B42" s="32" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="C42" s="32" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="E42" s="32">
         <v>2024</v>
@@ -5217,19 +5225,19 @@
       </c>
       <c r="I42" s="55">
         <f t="shared" ca="1" si="3"/>
-        <v>-0.18416666666666667</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="31"/>
       <c r="B43" s="33" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="D43" s="32" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="E43" s="32">
         <v>2025</v>
@@ -5251,13 +5259,13 @@
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="31"/>
       <c r="B44" s="33" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="C44" s="32" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="E44" s="32">
         <v>2026</v>
@@ -5273,18 +5281,18 @@
       </c>
       <c r="I44" s="55">
         <f ca="1">IF(H44&lt;&gt;0,ROUND((H44-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-6.6666666666666671E-3</v>
+        <v>-7.4999999999999997E-3</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B45" s="32" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="C45" s="32" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="E45" s="32">
         <v>2022</v>
@@ -5308,13 +5316,13 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B46" s="33" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="C46" s="32" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="E46" s="32">
         <v>2023</v>
@@ -5330,7 +5338,7 @@
       </c>
       <c r="I46" s="55">
         <f t="shared" ref="I46:I49" ca="1" si="4">IF(H46&lt;&gt;0,ROUND((H46-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.28500000000000003</v>
+        <v>-0.28583333333333333</v>
       </c>
       <c r="K46"/>
       <c r="L46" s="40"/>
@@ -5338,13 +5346,13 @@
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="31"/>
       <c r="B47" s="32" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="E47" s="32">
         <v>2024</v>
@@ -5360,19 +5368,19 @@
       </c>
       <c r="I47" s="55">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.21416666666666664</v>
+        <v>-0.215</v>
       </c>
       <c r="L47" s="40"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B48" s="33" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="E48" s="32">
         <v>2024</v>
@@ -5388,18 +5396,18 @@
       </c>
       <c r="I48" s="55">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.19166666666666665</v>
+        <v>-0.1925</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B49" s="33" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="E49" s="32">
         <v>2025</v>
@@ -5415,18 +5423,18 @@
       </c>
       <c r="I49" s="55">
         <f t="shared" ca="1" si="4"/>
-        <v>-8.4999999999999992E-2</v>
+        <v>-8.5833333333333345E-2</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B50" s="33" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="C50" s="32" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="E50" s="32">
         <v>2026</v>
@@ -5447,13 +5455,13 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" s="32" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="C51" s="32" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="E51" s="32">
         <v>2023</v>
@@ -5469,18 +5477,18 @@
       </c>
       <c r="I51" s="55">
         <f ca="1">IF(H51&lt;&gt;0,ROUND((H51-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.32749999999999996</v>
+        <v>-0.32833333333333331</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" s="32" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="C52" s="32" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="E52" s="32">
         <v>2023</v>
@@ -5496,18 +5504,18 @@
       </c>
       <c r="I52" s="55">
         <f t="shared" ref="I52:I54" ca="1" si="5">IF(H52&lt;&gt;0,ROUND((H52-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.29166666666666669</v>
+        <v>-0.29249999999999998</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" s="33" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="C53" s="32" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="E53" s="32">
         <v>2024</v>
@@ -5528,13 +5536,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B54" s="32" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="C54" s="32" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="E54" s="32">
         <v>2024</v>
@@ -5556,13 +5564,13 @@
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="31"/>
       <c r="B55" s="33" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="C55" s="33" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D55" s="33" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="E55" s="33">
         <v>2026</v>
@@ -5583,13 +5591,13 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B56" s="32" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="C56" s="32" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="E56" s="32" t="s">
         <v>6</v>
@@ -5605,18 +5613,18 @@
       </c>
       <c r="I56" s="55">
         <f ca="1">IF(H56&lt;&gt;0,ROUND((H56-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.16999999999999998</v>
+        <v>-0.17083333333333334</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" s="32" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="E57" s="32" t="s">
         <v>6</v>
@@ -5632,21 +5640,21 @@
       </c>
       <c r="I57" s="55">
         <f t="shared" ref="I57:I61" ca="1" si="6">IF(H57&lt;&gt;0,ROUND((H57-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.16999999999999998</v>
+        <v>-0.17083333333333334</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B58" s="32" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="C58" s="32" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="E58" s="53" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="F58" s="35" t="s">
         <v>6</v>
@@ -5659,21 +5667,21 @@
       </c>
       <c r="I58" s="55">
         <f t="shared" ca="1" si="6"/>
-        <v>-3.3333333333333335E-3</v>
+        <v>-4.1666666666666666E-3</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" s="32" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="C59" s="32" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="E59" s="53" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="F59" s="35" t="s">
         <v>6</v>
@@ -5686,21 +5694,21 @@
       </c>
       <c r="I59" s="55">
         <f t="shared" ca="1" si="6"/>
-        <v>-3.3333333333333335E-3</v>
+        <v>-4.1666666666666666E-3</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B60" s="32" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="C60" s="32" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="E60" s="53" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="F60" s="35" t="s">
         <v>6</v>
@@ -5713,21 +5721,21 @@
       </c>
       <c r="I60" s="55">
         <f t="shared" ca="1" si="6"/>
-        <v>-3.3333333333333335E-3</v>
+        <v>-4.1666666666666666E-3</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" s="32" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="E61" s="32" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F61" s="32">
         <v>499</v>
@@ -5746,16 +5754,16 @@
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="31"/>
       <c r="B62" s="33" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="C62" s="32" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="E62" s="32" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="F62" s="32">
         <v>2924</v>
@@ -5774,16 +5782,16 @@
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="31"/>
       <c r="B63" s="32" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="C63" s="32" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="E63" s="32" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F63" s="32">
         <v>6150</v>
@@ -5796,23 +5804,23 @@
       </c>
       <c r="I63" s="55">
         <f t="shared" ref="I63:I69" ca="1" si="7">IF(H63&lt;&gt;0,ROUND((H63-TODAY())/30,1)*(10%/12),"-")</f>
-        <v>-0.12583333333333332</v>
+        <v>-0.12666666666666665</v>
       </c>
       <c r="J63" s="47"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="31"/>
       <c r="B64" s="32" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="C64" s="32" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="D64" s="33" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="E64" s="32" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F64" s="32">
         <v>1305</v>
@@ -5825,22 +5833,22 @@
       </c>
       <c r="I64" s="55">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.12583333333333332</v>
+        <v>-0.12666666666666665</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="44"/>
       <c r="B65" s="33" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="C65" s="33" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="D65" s="33" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F65" s="33">
         <v>1434</v>
@@ -5859,13 +5867,13 @@
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="31"/>
       <c r="B66" s="35" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="D66" s="35" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="E66" s="35" t="s">
         <v>6</v>
@@ -5886,13 +5894,13 @@
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="31"/>
       <c r="B67" s="32" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="C67" s="32" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="E67" s="32" t="s">
         <v>6</v>
@@ -5914,13 +5922,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B68" s="33" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="C68" s="32" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="E68" s="32">
         <v>2023</v>
@@ -5942,13 +5950,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" s="32" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="C69" s="32" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="E69" s="32">
         <v>2023</v>
@@ -5964,12 +5972,12 @@
       </c>
       <c r="I69" s="55">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.28666666666666663</v>
+        <v>-0.28749999999999998</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="63" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="C70" s="64"/>
       <c r="D70" s="64"/>
